--- a/AAII_Financials/Quarterly/ADRNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ADRNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>ADRNY</t>
   </si>
@@ -656,73 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +763,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,8 +804,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +864,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +903,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +944,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +985,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1026,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,8 +1042,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1054,8 +1081,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,8 +1122,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1141,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1146,8 +1180,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1184,8 +1221,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,8 +1262,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1260,8 +1303,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1344,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1385,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1374,8 +1426,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1412,8 +1467,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1549,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1631,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,8 +1672,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1640,8 +1713,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,8 +1754,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1716,51 +1795,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,350 +1877,378 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3645100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4436600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4241200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4456300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4615100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5133200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6433400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4559600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6248800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7031000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3851000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5044500</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E42" s="3">
         <v>17300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>101200</v>
-      </c>
-      <c r="F42" s="3">
-        <v>16400</v>
       </c>
       <c r="G42" s="3">
         <v>16400</v>
       </c>
       <c r="H42" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I42" s="3">
         <v>17300</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>16700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17300</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3216200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3081800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3447100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2977100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2923300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2650600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3073300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2844700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2740800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2655100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2946800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2364500</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5676300</v>
+      </c>
+      <c r="E44" s="3">
         <v>5698200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5640000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5754200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5745800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5402900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5002600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5039600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5125900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5025400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5065800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5159800</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>442500</v>
+      </c>
+      <c r="E45" s="3">
         <v>449300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>196500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>532000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>543600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>493900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>250300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>405000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>439900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>529200</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13419300</v>
+      </c>
+      <c r="E46" s="3">
         <v>14177400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14027100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14195500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14281200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14152900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15148600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13312500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14956600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15559400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12670500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13542500</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>278300</v>
+      </c>
+      <c r="E47" s="3">
         <v>281100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>304700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>300500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>297600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>277300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>291000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>302600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>278600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>274000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>326100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>278400</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24547200</v>
+      </c>
+      <c r="E48" s="3">
         <v>24619800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25050600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24446900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24469800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23771700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22734400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22969700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22844700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22939900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23586800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23210200</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15861100</v>
+      </c>
+      <c r="E49" s="3">
         <v>15956200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16078800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16011500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16019900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15443000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13995200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14407700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14159400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14213000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14367200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14062200</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2326,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2367700</v>
+      </c>
+      <c r="E52" s="3">
         <v>2262700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1178800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2207700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2155800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1959500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>970900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1970500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1881500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1945200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>967200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1742200</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2408,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56636600</v>
+      </c>
+      <c r="E54" s="3">
         <v>57458500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>57751800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>57329300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>57394300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>55766900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54064000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53159500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>54321200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55144000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>52858400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>53080000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,236 +2485,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10249800</v>
+      </c>
+      <c r="E57" s="3">
         <v>9729300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10598800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9805900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10083200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9242900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8889400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8645800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8867500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8664400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9150000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8347800</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4134400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3827200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3884700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5650100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5259500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5085600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4514500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3743400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4416600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4663900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3410000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4443400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4798400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1089400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4742800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4565900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4523400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>960500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4535000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4224800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4480500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>839000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4562900</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18827600</v>
+      </c>
+      <c r="E60" s="3">
         <v>18354800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19757600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20198800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19908600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18851800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18141600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16924200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17508800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17808800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17254300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18125500</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17833000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18546100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17782400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17556100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17652000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16983300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16692000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17197700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17604200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17697700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16249600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16048900</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1545400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1577200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1352900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1535300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1495000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1459100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1381800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1371000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1246100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1211600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1118600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1096500</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +2852,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40162000</v>
+      </c>
+      <c r="E66" s="3">
         <v>40419400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41051800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41120200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40864700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39058700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37947600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37133000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38106700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38697800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36549100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36862800</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,8 +3074,11 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2941,8 +3115,11 @@
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3238,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16474700</v>
+      </c>
+      <c r="E76" s="3">
         <v>17039200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16700000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16209100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16529600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16708200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16116400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16026600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16214500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16446200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16309300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16217200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,51 +3320,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3212,8 +3407,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3426,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1041600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1006300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>390000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>955700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>940700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>926700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>474200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>920800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>937800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>946300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>493700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>874700</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3670,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1987900</v>
+      </c>
+      <c r="E89" s="3">
         <v>872100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3177600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1633500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1867600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1403800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2418400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1484900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1480800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1288200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2464900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1527300</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3730,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-715100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-694700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-892900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-675900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-724100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-659700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-688300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-588400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-593600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-602000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-883200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-580000</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3851,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-649000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-617500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-741200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-597500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-704200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1992000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-568400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-476700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-483200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-329100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-935100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-477300</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,46 +3911,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>734500</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>537900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>715900</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>518000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>614000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>497500</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4073,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2099700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-42600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1197400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1855900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-838400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>113700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2840200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1757200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2258100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2813100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-235000</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-130000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>209600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-121700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>26800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>55000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-130400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>106900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-29300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-297100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>167700</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-727600</v>
+      </c>
+      <c r="E102" s="3">
         <v>282300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-284700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-154300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-938500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1556500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2173300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1953800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-732900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3272200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1413700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>921900</v>
       </c>
     </row>
